--- a/Dashboard Kinerja Operasional Gudang.xlsx
+++ b/Dashboard Kinerja Operasional Gudang.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MyBook Hype AMD\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF4D59F-6EE0-472B-BD1A-C537C0ECA959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB93F570-5B2A-4DB9-8DBD-342FFF940E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1060,13 +1060,25 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1077,12 +1089,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1097,12 +1103,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1130,6 +1130,24 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;Rp&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;Rp&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="&quot;Rp&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="&quot;Rp&quot;#,##0"/>
@@ -1169,24 +1187,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="22" formatCode="mmm\-yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;Rp&quot;#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;Rp&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;Rp&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10323,146 +10323,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{854F2077-4B88-4979-9293-5B7D4FCAB11D}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A47:E53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="28">
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="3" outline="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="4"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="3" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="3" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="17" outline="0" showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="3" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="167" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="168" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-    <i i="3">
-      <x v="3"/>
-    </i>
-  </colItems>
-  <dataFields count="4">
-    <dataField name="Count of Transaction_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Quantity" fld="6" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Damaged_Qty" fld="10" baseField="0" baseItem="0"/>
-    <dataField name="Average of Processing_Time_Hours" fld="11" subtotal="average" baseField="7" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="16">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-          <reference field="7" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9AAA098-7E68-48C2-AC6C-7A9B848FBF41}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A9AAA098-7E68-48C2-AC6C-7A9B848FBF41}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A37:E43" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="28">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -10577,7 +10438,7 @@
     <dataField name="Sum of Transaction_Value" fld="14" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="17">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -10600,8 +10461,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47FE796B-7E62-4E7F-9FB3-9C43ED59696A}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47FE796B-7E62-4E7F-9FB3-9C43ED59696A}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A14:E23" firstHeaderRow="0" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="28">
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -10951,8 +10812,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C8656B6-7EA3-4B5B-BB27-FEB5C3EC592F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C8656B6-7EA3-4B5B-BB27-FEB5C3EC592F}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A73:D77" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="28">
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
@@ -11055,7 +10916,7 @@
     <dataField name="Average of Processing_Time_Hours" fld="11" subtotal="average" baseField="12" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="18">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="2">
           <reference field="4294967294" count="1" selected="0">
@@ -11078,8 +10939,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4BC7ADD5-E4AE-408D-85B9-FD88690F73A2}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4BC7ADD5-E4AE-408D-85B9-FD88690F73A2}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:J10" firstHeaderRow="0" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="28">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -11575,7 +11436,7 @@
     <dataField name="Average of Processing_Time_Hours" fld="11" subtotal="average" baseField="27" baseItem="4" numFmtId="164"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="21">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -11584,7 +11445,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="6">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -11593,7 +11454,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="5">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -11615,8 +11476,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A85A1BE-042A-4D5B-910C-B7AC1EBED25A}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5A85A1BE-042A-4D5B-910C-B7AC1EBED25A}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A57:E66" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="28">
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
@@ -11754,6 +11615,145 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{854F2077-4B88-4979-9293-5B7D4FCAB11D}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A47:E53" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="28">
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="3" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="3" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="3" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="17" outline="0" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="3" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="167" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="168" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="166" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="Count of Transaction_ID" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Quantity" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Damaged_Qty" fld="10" baseField="0" baseItem="0"/>
+    <dataField name="Average of Processing_Time_Hours" fld="11" subtotal="average" baseField="7" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="8">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="7" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="WarehouseTransactions" displayName="WarehouseTransactions" ref="A1:M101" totalsRowShown="0">
   <autoFilter ref="A1:M101" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
@@ -11793,43 +11793,43 @@
     <tableColumn id="11" xr3:uid="{B43A6B7C-96F0-43F4-84A6-998A7407DF8F}" name="Damaged_Qty"/>
     <tableColumn id="12" xr3:uid="{832B88AE-0BC7-4FB2-871D-078A66A049E1}" name="Processing_Time_Hours"/>
     <tableColumn id="13" xr3:uid="{D59A663E-781F-400B-A5B4-C4035D3A86AC}" name="Status"/>
-    <tableColumn id="14" xr3:uid="{657D5FDA-0350-469F-A76A-D936E72C3FC8}" name="Month" dataDxfId="15">
+    <tableColumn id="14" xr3:uid="{657D5FDA-0350-469F-A76A-D936E72C3FC8}" name="Month" dataDxfId="21">
       <calculatedColumnFormula>DATE(YEAR(WarehouseTransactions3[[#This Row],[Date]]),MONTH(WarehouseTransactions3[[#This Row],[Date]]),1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{34A5B896-405A-441E-83D0-A56840357883}" name="Transaction_Value" dataDxfId="14">
+    <tableColumn id="15" xr3:uid="{34A5B896-405A-441E-83D0-A56840357883}" name="Transaction_Value" dataDxfId="20">
       <calculatedColumnFormula>WarehouseTransactions3[[#This Row],[Quantity]]*WarehouseTransactions3[[#This Row],[Unit_Cost]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{E69C892F-A2F8-4AA9-BE39-023F7B324E37}" name="Net_Good_Qty" dataDxfId="13">
+    <tableColumn id="16" xr3:uid="{E69C892F-A2F8-4AA9-BE39-023F7B324E37}" name="Net_Good_Qty" dataDxfId="19">
       <calculatedColumnFormula>WarehouseTransactions3[[#This Row],[Quantity]]-WarehouseTransactions3[[#This Row],[Damaged_Qty]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{C2B07266-0578-430C-B249-42300A7EB173}" name="Signed_Quantity" dataDxfId="12">
+    <tableColumn id="17" xr3:uid="{C2B07266-0578-430C-B249-42300A7EB173}" name="Signed_Quantity" dataDxfId="18">
       <calculatedColumnFormula>IF(WarehouseTransactions3[[#This Row],[Transaction_Type]]="Inbound",WarehouseTransactions3[[#This Row],[Quantity]],-WarehouseTransactions3[[#This Row],[Quantity]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{F023EA2A-963C-4E19-9D4A-BA97F7356C1E}" name="Damage_Rate" dataDxfId="11">
+    <tableColumn id="18" xr3:uid="{F023EA2A-963C-4E19-9D4A-BA97F7356C1E}" name="Damage_Rate" dataDxfId="17">
       <calculatedColumnFormula>IFERROR(WarehouseTransactions3[[#This Row],[Damaged_Qty]]/WarehouseTransactions3[[#This Row],[Quantity]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{5EA28F61-9E1A-4E5A-B39F-4BE07EDDC302}" name="Delayed_Flag" dataDxfId="10">
+    <tableColumn id="19" xr3:uid="{5EA28F61-9E1A-4E5A-B39F-4BE07EDDC302}" name="Delayed_Flag" dataDxfId="16">
       <calculatedColumnFormula>IF(WarehouseTransactions3[[#This Row],[Status]]="Delayed",1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{62DAF41A-A349-49C9-A26D-B9395FA4F91F}" name="Pending_Flag" dataDxfId="9">
+    <tableColumn id="20" xr3:uid="{62DAF41A-A349-49C9-A26D-B9395FA4F91F}" name="Pending_Flag" dataDxfId="15">
       <calculatedColumnFormula>IF(WarehouseTransactions3[[#This Row],[Status]]="Pending",1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{606F5E49-CF7F-4169-A6A3-D530692E7272}" name="High_Process_Flag" dataDxfId="8">
+    <tableColumn id="21" xr3:uid="{606F5E49-CF7F-4169-A6A3-D530692E7272}" name="High_Process_Flag" dataDxfId="14">
       <calculatedColumnFormula>IF(WarehouseTransactions3[[#This Row],[Processing_Time_Hours]]&gt;8,1,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{CD7A6EA4-9BE6-4BE7-B6E3-952B62775147}" name="Column1" dataDxfId="7">
+    <tableColumn id="22" xr3:uid="{CD7A6EA4-9BE6-4BE7-B6E3-952B62775147}" name="Column1" dataDxfId="13">
       <calculatedColumnFormula>WarehouseTransactions3[[#This Row],[Processing_Time_Hours]]/24</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{1F40EC6E-07CB-4741-ACCB-6E073BD114C6}" name="Inbound_Qty" dataDxfId="6">
+    <tableColumn id="23" xr3:uid="{1F40EC6E-07CB-4741-ACCB-6E073BD114C6}" name="Inbound_Qty" dataDxfId="12">
       <calculatedColumnFormula>IF(WarehouseTransactions3[[#This Row],[Transaction_Type]]="Inbound",WarehouseTransactions3[[#This Row],[Quantity]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{B3762FDC-328E-4573-A2B6-DBE7331990EA}" name="Outbound_Qty" dataDxfId="5">
+    <tableColumn id="24" xr3:uid="{B3762FDC-328E-4573-A2B6-DBE7331990EA}" name="Outbound_Qty" dataDxfId="11">
       <calculatedColumnFormula>IF(WarehouseTransactions3[[#This Row],[Transaction_Type]]="Outbound",WarehouseTransactions3[[#This Row],[Quantity]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{14208DCE-D793-4AB1-9A05-DFE2ACCC6F6B}" name="Inbound_Value" dataDxfId="4">
+    <tableColumn id="25" xr3:uid="{14208DCE-D793-4AB1-9A05-DFE2ACCC6F6B}" name="Inbound_Value" dataDxfId="10">
       <calculatedColumnFormula>IF(WarehouseTransactions3[[#This Row],[Transaction_Type]]="Inbound",WarehouseTransactions3[[#This Row],[Transaction_Value]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{8DD65BDE-28B1-4393-997E-4CF385E75495}" name="Outbound_Value" dataDxfId="3">
+    <tableColumn id="26" xr3:uid="{8DD65BDE-28B1-4393-997E-4CF385E75495}" name="Outbound_Value" dataDxfId="9">
       <calculatedColumnFormula>IF(WarehouseTransactions3[[#This Row],[Transaction_Type]]="Outbound",WarehouseTransactions3[[#This Row],[Transaction_Value]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -26604,46 +26604,46 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:38" ht="21" x14ac:dyDescent="0.4">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="41" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="36"/>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.3">
       <c r="S4" s="21" t="s">
@@ -26690,41 +26690,41 @@
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="43" t="s">
         <v>218</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="E5" s="43" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="E5" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="I5" s="45" t="s">
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="I5" s="32" t="s">
         <v>211</v>
       </c>
-      <c r="J5" s="46"/>
-      <c r="K5" s="46"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
     </row>
     <row r="6" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="38">
+      <c r="A6" s="34">
         <f>SUMIF(Analysis_Data!F2:F101,"Inbound",Analysis_Data!G2:G101)</f>
         <v>2986</v>
       </c>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="E6" s="39">
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="E6" s="35">
         <f>SUMIF(Analysis_Data!F2:F101,"Outbound",Analysis_Data!G2:G101)</f>
         <v>2718</v>
       </c>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="I6" s="40">
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="I6" s="42">
         <f>A6-E6</f>
         <v>268</v>
       </c>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
       <c r="S6" s="31" t="s">
         <v>227</v>
       </c>
@@ -26782,15 +26782,15 @@
       </c>
     </row>
     <row r="7" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="40"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
       <c r="S7" s="31" t="s">
         <v>228</v>
       </c>
@@ -26835,15 +26835,15 @@
       </c>
     </row>
     <row r="8" spans="1:38" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="40"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
       <c r="S8" s="31" t="s">
         <v>229</v>
       </c>
@@ -26888,21 +26888,21 @@
       </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="43" t="s">
         <v>212</v>
       </c>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="E9" s="43" t="s">
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="E9" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="I9" s="45" t="s">
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="I9" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="J9" s="46"/>
-      <c r="K9" s="46"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
       <c r="S9" s="31" t="s">
         <v>230</v>
       </c>
@@ -26941,24 +26941,24 @@
       </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A10" s="38">
+      <c r="A10" s="34">
         <f>SUMIF(Analysis_Data!F2:F101,"Inbound",Analysis_Data!O2:O101)</f>
         <v>60591600</v>
       </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="E10" s="39">
+      <c r="B10" s="34"/>
+      <c r="C10" s="34"/>
+      <c r="E10" s="35">
         <f>SUMIF(Analysis_Data!F2:F101,"Outbound",Analysis_Data!O2:O101)</f>
         <v>52379500</v>
       </c>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="I10" s="34">
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="I10" s="36">
         <f>IFERROR(SUM(Analysis_Data!K2:K101)/SUM(Analysis_Data!G2:G101),0)</f>
         <v>5.9607293127629732E-3</v>
       </c>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
       <c r="S10" s="31" t="s">
         <v>231</v>
       </c>
@@ -26997,15 +26997,15 @@
       </c>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A11" s="38"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
       <c r="S11" s="31" t="s">
         <v>232</v>
       </c>
@@ -27029,15 +27029,15 @@
       </c>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="34"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
       <c r="W12" t="str">
         <v>Pulpen Gel Hitam</v>
       </c>
@@ -27052,21 +27052,21 @@
       </c>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="43" t="s">
         <v>215</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="E13" s="43" t="s">
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="E13" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="I13" s="45" t="s">
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="I13" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
       <c r="W13" t="str">
         <v>Teh Celup 25 Sachet</v>
       </c>
@@ -27081,56 +27081,54 @@
       </c>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A14" s="32">
+      <c r="A14" s="37">
         <f>COUNTIF(Analysis_Data!M2:M101,"Delayed")</f>
         <v>10</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="E14" s="33">
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="E14" s="38">
         <f>COUNTIF(Analysis_Data!M2:M101,"Pending")</f>
         <v>10</v>
       </c>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="I14" s="34">
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="I14" s="36">
         <f>COUNTIF(Analysis_Data!M2:M101,"Completed")/COUNTA(Analysis_Data!A2:A101)</f>
         <v>0.8</v>
       </c>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="36"/>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="36"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="A10:C12"/>
-    <mergeCell ref="E10:G12"/>
-    <mergeCell ref="I10:K12"/>
-    <mergeCell ref="A14:C16"/>
-    <mergeCell ref="E14:G16"/>
-    <mergeCell ref="I14:K16"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="E13:G13"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A6:C8"/>
@@ -27139,11 +27137,13 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="I5:K5"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="A10:C12"/>
+    <mergeCell ref="E10:G12"/>
+    <mergeCell ref="I10:K12"/>
+    <mergeCell ref="A14:C16"/>
+    <mergeCell ref="E14:G16"/>
+    <mergeCell ref="I14:K16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
